--- a/Assets/Data/Excel/BuildingLevelData.xlsx
+++ b/Assets/Data/Excel/BuildingLevelData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <r>
       <rPr>
@@ -42,7 +42,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">levelId</t>
+    <t xml:space="preserve">Id</t>
   </si>
   <si>
     <t xml:space="preserve">DisplayName</t>
@@ -139,6 +139,9 @@
       </rPr>
       <t xml:space="preserve">id</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">d</t>
   </si>
   <si>
     <t xml:space="preserve">sd</t>
@@ -473,11 +476,14 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
@@ -508,11 +514,14 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>2</v>
@@ -543,11 +552,14 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>3</v>

--- a/Assets/Data/Excel/BuildingLevelData.xlsx
+++ b/Assets/Data/Excel/BuildingLevelData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <r>
       <rPr>
@@ -48,6 +48,9 @@
     <t xml:space="preserve">DisplayName</t>
   </si>
   <si>
+    <t xml:space="preserve">PoolId</t>
+  </si>
+  <si>
     <t xml:space="preserve">block</t>
   </si>
   <si>
@@ -61,6 +64,9 @@
   </si>
   <si>
     <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgradeTime</t>
   </si>
   <si>
     <t xml:space="preserve">damage</t>
@@ -383,10 +389,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -399,10 +406,10 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="3"/>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
@@ -415,10 +422,10 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -427,173 +434,203 @@
       <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" s="1" t="n">
+      <c r="O4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="I5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="K5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="P5" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="H6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="L14" s="1"/>
+      <c r="N14" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
